--- a/corpus/C12.xlsx
+++ b/corpus/C12.xlsx
@@ -498,7 +498,7 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2597</v>
+        <v>0.02597</v>
       </c>
     </row>
     <row r="12">
@@ -773,55 +773,55 @@
       </c>
       <c r="N5">
         <f>M9</f>
-        <v>13900.0</v>
+        <v>13293.0</v>
       </c>
       <c r="O5">
         <f>N9</f>
-        <v>14567.0</v>
+        <v>13931.0</v>
       </c>
       <c r="P5">
         <f>O9</f>
-        <v>15266.0</v>
+        <v>14600.0</v>
       </c>
       <c r="Q5">
         <f>P9</f>
-        <v>15999.0</v>
+        <v>15301.0</v>
       </c>
       <c r="R5">
         <f>Q9</f>
-        <v>16767.0</v>
+        <v>16035.0</v>
       </c>
       <c r="S5">
         <f>R9</f>
-        <v>17572.0</v>
+        <v>16805.0</v>
       </c>
       <c r="T5">
         <f>S9</f>
-        <v>18416.0</v>
+        <v>17611.0</v>
       </c>
       <c r="U5">
         <f>T9</f>
-        <v>19300.0</v>
+        <v>18456.0</v>
       </c>
       <c r="V5">
         <f>U9</f>
-        <v>20226.0</v>
+        <v>19342.0</v>
       </c>
       <c r="W5">
         <f>V9</f>
-        <v>21197.0</v>
+        <v>20271.0</v>
       </c>
       <c r="X5">
         <f>W9</f>
-        <v>22214.0</v>
+        <v>21244.0</v>
       </c>
       <c r="Y5">
         <f>X9</f>
-        <v>23281.0</v>
+        <v>22264.0</v>
       </c>
       <c r="Z5">
         <f>Y9</f>
-        <v>24398.0</v>
+        <v>23333.0</v>
       </c>
     </row>
     <row r="6">
@@ -876,55 +876,55 @@
       </c>
       <c r="N6">
         <f>ROUND(N5*Assumptions!$B$5,0)</f>
-        <v>895.0</v>
+        <v>856.0</v>
       </c>
       <c r="O6">
         <f>ROUND(O5*Assumptions!$B$5,0)</f>
-        <v>938.0</v>
+        <v>897.0</v>
       </c>
       <c r="P6">
         <f>ROUND(P5*Assumptions!$B$5,0)</f>
-        <v>983.0</v>
+        <v>940.0</v>
       </c>
       <c r="Q6">
         <f>ROUND(Q5*Assumptions!$B$5,0)</f>
-        <v>1030.0</v>
+        <v>985.0</v>
       </c>
       <c r="R6">
         <f>ROUND(R5*Assumptions!$B$5,0)</f>
-        <v>1080.0</v>
+        <v>1033.0</v>
       </c>
       <c r="S6">
         <f>ROUND(S5*Assumptions!$B$5,0)</f>
-        <v>1132.0</v>
+        <v>1082.0</v>
       </c>
       <c r="T6">
         <f>ROUND(T5*Assumptions!$B$5,0)</f>
-        <v>1186.0</v>
+        <v>1134.0</v>
       </c>
       <c r="U6">
         <f>ROUND(U5*Assumptions!$B$5,0)</f>
-        <v>1243.0</v>
+        <v>1189.0</v>
       </c>
       <c r="V6">
         <f>ROUND(V5*Assumptions!$B$5,0)</f>
-        <v>1303.0</v>
+        <v>1246.0</v>
       </c>
       <c r="W6">
         <f>ROUND(W5*Assumptions!$B$5,0)</f>
-        <v>1365.0</v>
+        <v>1305.0</v>
       </c>
       <c r="X6">
         <f>ROUND(X5*Assumptions!$B$5,0)</f>
-        <v>1431.0</v>
+        <v>1368.0</v>
       </c>
       <c r="Y6">
         <f>ROUND(Y5*Assumptions!$B$5,0)</f>
-        <v>1499.0</v>
+        <v>1434.0</v>
       </c>
       <c r="Z6">
         <f>ROUND(Z5*Assumptions!$B$5,0)</f>
-        <v>1571.0</v>
+        <v>1503.0</v>
       </c>
     </row>
     <row r="7">
@@ -979,55 +979,55 @@
       </c>
       <c r="N7">
         <f>-ROUND(N5*Assumptions!$B$6,0)</f>
-        <v>-228.0</v>
+        <v>-218.0</v>
       </c>
       <c r="O7">
         <f>-ROUND(O5*Assumptions!$B$6,0)</f>
-        <v>-239.0</v>
+        <v>-228.0</v>
       </c>
       <c r="P7">
         <f>-ROUND(P5*Assumptions!$B$6,0)</f>
-        <v>-250.0</v>
+        <v>-239.0</v>
       </c>
       <c r="Q7">
         <f>-ROUND(Q5*Assumptions!$B$6,0)</f>
-        <v>-262.0</v>
+        <v>-251.0</v>
       </c>
       <c r="R7">
         <f>-ROUND(R5*Assumptions!$B$6,0)</f>
-        <v>-275.0</v>
+        <v>-263.0</v>
       </c>
       <c r="S7">
         <f>-ROUND(S5*Assumptions!$B$6,0)</f>
-        <v>-288.0</v>
+        <v>-276.0</v>
       </c>
       <c r="T7">
         <f>-ROUND(T5*Assumptions!$B$6,0)</f>
-        <v>-302.0</v>
+        <v>-289.0</v>
       </c>
       <c r="U7">
         <f>-ROUND(U5*Assumptions!$B$6,0)</f>
-        <v>-317.0</v>
+        <v>-303.0</v>
       </c>
       <c r="V7">
         <f>-ROUND(V5*Assumptions!$B$6,0)</f>
-        <v>-332.0</v>
+        <v>-317.0</v>
       </c>
       <c r="W7">
         <f>-ROUND(W5*Assumptions!$B$6,0)</f>
-        <v>-348.0</v>
+        <v>-332.0</v>
       </c>
       <c r="X7">
         <f>-ROUND(X5*Assumptions!$B$6,0)</f>
-        <v>-364.0</v>
+        <v>-348.0</v>
       </c>
       <c r="Y7">
         <f>-ROUND(Y5*Assumptions!$B$6,0)</f>
-        <v>-382.0</v>
+        <v>-365.0</v>
       </c>
       <c r="Z7">
         <f>-ROUND(Z5*Assumptions!$B$6,0)</f>
-        <v>-400.0</v>
+        <v>-383.0</v>
       </c>
     </row>
     <row r="9">
@@ -1077,60 +1077,60 @@
         <v>13264.0</v>
       </c>
       <c r="M9">
-        <f>M5+M6+M7</f>
-        <v>13900.0</v>
+        <f>L5+M6+M7</f>
+        <v>13293.0</v>
       </c>
       <c r="N9">
         <f>N5+N6+N7</f>
-        <v>14567.0</v>
+        <v>13931.0</v>
       </c>
       <c r="O9">
         <f>O5+O6+O7</f>
-        <v>15266.0</v>
+        <v>14600.0</v>
       </c>
       <c r="P9">
         <f>P5+P6+P7</f>
-        <v>15999.0</v>
+        <v>15301.0</v>
       </c>
       <c r="Q9">
         <f>Q5+Q6+Q7</f>
-        <v>16767.0</v>
+        <v>16035.0</v>
       </c>
       <c r="R9">
         <f>R5+R6+R7</f>
-        <v>17572.0</v>
+        <v>16805.0</v>
       </c>
       <c r="S9">
         <f>S5+S6+S7</f>
-        <v>18416.0</v>
+        <v>17611.0</v>
       </c>
       <c r="T9">
         <f>T5+T6+T7</f>
-        <v>19300.0</v>
+        <v>18456.0</v>
       </c>
       <c r="U9">
         <f>U5+U6+U7</f>
-        <v>20226.0</v>
+        <v>19342.0</v>
       </c>
       <c r="V9">
         <f>V5+V6+V7</f>
-        <v>21197.0</v>
+        <v>20271.0</v>
       </c>
       <c r="W9">
         <f>W5+W6+W7</f>
-        <v>22214.0</v>
+        <v>21244.0</v>
       </c>
       <c r="X9">
         <f>X5+X6+X7</f>
-        <v>23281.0</v>
+        <v>22264.0</v>
       </c>
       <c r="Y9">
         <f>Y5+Y6+Y7</f>
-        <v>24398.0</v>
+        <v>23333.0</v>
       </c>
       <c r="Z9">
         <f>Z5+Z6+Z7</f>
-        <v>25569.0</v>
+        <v>24453.0</v>
       </c>
     </row>
     <row r="11">
@@ -1284,59 +1284,59 @@
       </c>
       <c r="M13">
         <f>ROUND((M5+M9)/2,0)</f>
-        <v>13582.0</v>
+        <v>13279.0</v>
       </c>
       <c r="N13">
         <f>ROUND((N5+N9)/2,0)</f>
-        <v>14234.0</v>
+        <v>13612.0</v>
       </c>
       <c r="O13">
         <f>ROUND((O5+O9)/2,0)</f>
-        <v>14917.0</v>
+        <v>14266.0</v>
       </c>
       <c r="P13">
         <f>ROUND((P5+P9)/2,0)</f>
-        <v>15633.0</v>
+        <v>14951.0</v>
       </c>
       <c r="Q13">
         <f>ROUND((Q5+Q9)/2,0)</f>
-        <v>16383.0</v>
+        <v>15668.0</v>
       </c>
       <c r="R13">
         <f>ROUND((R5+R9)/2,0)</f>
-        <v>17170.0</v>
+        <v>16420.0</v>
       </c>
       <c r="S13">
         <f>ROUND((S5+S9)/2,0)</f>
-        <v>17994.0</v>
+        <v>17208.0</v>
       </c>
       <c r="T13">
         <f>ROUND((T5+T9)/2,0)</f>
-        <v>18858.0</v>
+        <v>18034.0</v>
       </c>
       <c r="U13">
         <f>ROUND((U5+U9)/2,0)</f>
-        <v>19763.0</v>
+        <v>18899.0</v>
       </c>
       <c r="V13">
         <f>ROUND((V5+V9)/2,0)</f>
-        <v>20712.0</v>
+        <v>19807.0</v>
       </c>
       <c r="W13">
         <f>ROUND((W5+W9)/2,0)</f>
-        <v>21706.0</v>
+        <v>20758.0</v>
       </c>
       <c r="X13">
         <f>ROUND((X5+X9)/2,0)</f>
-        <v>22748.0</v>
+        <v>21754.0</v>
       </c>
       <c r="Y13">
         <f>ROUND((Y5+Y9)/2,0)</f>
-        <v>23840.0</v>
+        <v>22799.0</v>
       </c>
       <c r="Z13">
         <f>ROUND((Z5+Z9)/2,0)</f>
-        <v>24984.0</v>
+        <v>23893.0</v>
       </c>
     </row>
     <row r="15">
@@ -1387,59 +1387,59 @@
       </c>
       <c r="M15">
         <f>ROUND(M13*M11,0)</f>
-        <v>974237.0</v>
+        <v>952503.0</v>
       </c>
       <c r="N15">
         <f>ROUND(N13*N11,0)</f>
-        <v>1027125.0</v>
+        <v>982242.0</v>
       </c>
       <c r="O15">
         <f>ROUND(O13*O11,0)</f>
-        <v>1082825.0</v>
+        <v>1035569.0</v>
       </c>
       <c r="P15">
         <f>ROUND(P13*P11,0)</f>
-        <v>1141678.0</v>
+        <v>1091872.0</v>
       </c>
       <c r="Q15">
         <f>ROUND(Q13*Q11,0)</f>
-        <v>1203659.0</v>
+        <v>1151128.0</v>
       </c>
       <c r="R15">
         <f>ROUND(R13*R11,0)</f>
-        <v>1269035.0</v>
+        <v>1213602.0</v>
       </c>
       <c r="S15">
         <f>ROUND(S13*S11,0)</f>
-        <v>1337854.0</v>
+        <v>1279415.0</v>
       </c>
       <c r="T15">
         <f>ROUND(T13*T11,0)</f>
-        <v>1410578.0</v>
+        <v>1348943.0</v>
       </c>
       <c r="U15">
         <f>ROUND(U13*U11,0)</f>
-        <v>1487166.0</v>
+        <v>1422150.0</v>
       </c>
       <c r="V15">
         <f>ROUND(V13*V11,0)</f>
-        <v>1567898.0</v>
+        <v>1499390.0</v>
       </c>
       <c r="W15">
         <f>ROUND(W13*W11,0)</f>
-        <v>1652912.0</v>
+        <v>1580722.0</v>
       </c>
       <c r="X15">
         <f>ROUND(X13*X11,0)</f>
-        <v>1742724.0</v>
+        <v>1666574.0</v>
       </c>
       <c r="Y15">
         <f>ROUND(Y13*Y11,0)</f>
-        <v>1837349.0</v>
+        <v>1757119.0</v>
       </c>
       <c r="Z15">
         <f>ROUND(Z13*Z11,0)</f>
-        <v>1937010.0</v>
+        <v>1852424.0</v>
       </c>
     </row>
     <row r="17">
@@ -1490,59 +1490,59 @@
       </c>
       <c r="M17">
         <f>L17+M15</f>
-        <v>8342552.0</v>
+        <v>8320818.0</v>
       </c>
       <c r="N17">
         <f>M17+N15</f>
-        <v>9369677.0</v>
+        <v>9303060.0</v>
       </c>
       <c r="O17">
         <f>N17+O15</f>
-        <v>10452502.0</v>
+        <v>10338629.0</v>
       </c>
       <c r="P17">
         <f>O17+P15</f>
-        <v>11594180.0</v>
+        <v>11430501.0</v>
       </c>
       <c r="Q17">
         <f>P17+Q15</f>
-        <v>12797839.0</v>
+        <v>12581629.0</v>
       </c>
       <c r="R17">
         <f>Q17+R15</f>
-        <v>14066874.0</v>
+        <v>13795231.0</v>
       </c>
       <c r="S17">
         <f>R17+S15</f>
-        <v>15404728.0</v>
+        <v>15074646.0</v>
       </c>
       <c r="T17">
         <f>S17+T15</f>
-        <v>16815306.0</v>
+        <v>16423589.0</v>
       </c>
       <c r="U17">
         <f>T17+U15</f>
-        <v>18302472.0</v>
+        <v>17845739.0</v>
       </c>
       <c r="V17">
         <f>U17+V15</f>
-        <v>19870370.0</v>
+        <v>19345129.0</v>
       </c>
       <c r="W17">
         <f>V17+W15</f>
-        <v>21523282.0</v>
+        <v>20925851.0</v>
       </c>
       <c r="X17">
         <f>W17+X15</f>
-        <v>23266006.0</v>
+        <v>22592425.0</v>
       </c>
       <c r="Y17">
         <f>X17+Y15</f>
-        <v>25103355.0</v>
+        <v>24349544.0</v>
       </c>
       <c r="Z17">
         <f>Y17+Z15</f>
-        <v>27040365.0</v>
+        <v>26201968.0</v>
       </c>
     </row>
   </sheetData>
@@ -2089,99 +2089,99 @@
       </c>
       <c r="C10">
         <f>ROUND(Revenue!C15*Assumptions!$B$11,0)</f>
-        <v>149113.0</v>
+        <v>14911.0</v>
       </c>
       <c r="D10">
         <f>ROUND(Revenue!D15*Assumptions!$B$11,0)</f>
-        <v>157219.0</v>
+        <v>15722.0</v>
       </c>
       <c r="E10">
         <f>ROUND(Revenue!E15*Assumptions!$B$11,0)</f>
-        <v>165749.0</v>
+        <v>16575.0</v>
       </c>
       <c r="F10">
         <f>ROUND(Revenue!F15*Assumptions!$B$11,0)</f>
-        <v>174728.0</v>
+        <v>17473.0</v>
       </c>
       <c r="G10">
         <f>ROUND(Revenue!G15*Assumptions!$B$11,0)</f>
-        <v>184215.0</v>
+        <v>18421.0</v>
       </c>
       <c r="H10">
         <f>ROUND(Revenue!H15*Assumptions!$B$11,0)</f>
-        <v>194227.0</v>
+        <v>19423.0</v>
       </c>
       <c r="I10">
         <f>ROUND(Revenue!I15*Assumptions!$B$11,0)</f>
-        <v>204783.0</v>
+        <v>20478.0</v>
       </c>
       <c r="J10">
         <f>ROUND(Revenue!J15*Assumptions!$B$11,0)</f>
-        <v>215909.0</v>
+        <v>21591.0</v>
       </c>
       <c r="K10">
         <f>ROUND(Revenue!K15*Assumptions!$B$11,0)</f>
-        <v>227614.0</v>
+        <v>22761.0</v>
       </c>
       <c r="L10">
         <f>ROUND(Revenue!L15*Assumptions!$B$11,0)</f>
-        <v>239994.0</v>
+        <v>23999.0</v>
       </c>
       <c r="M10">
         <f>ROUND(Revenue!M15*Assumptions!$B$11,0)</f>
-        <v>253009.0</v>
+        <v>24737.0</v>
       </c>
       <c r="N10">
         <f>ROUND(Revenue!N15*Assumptions!$B$11,0)</f>
-        <v>266744.0</v>
+        <v>25509.0</v>
       </c>
       <c r="O10">
         <f>ROUND(Revenue!O15*Assumptions!$B$11,0)</f>
-        <v>281210.0</v>
+        <v>26894.0</v>
       </c>
       <c r="P10">
         <f>ROUND(Revenue!P15*Assumptions!$B$11,0)</f>
-        <v>296494.0</v>
+        <v>28356.0</v>
       </c>
       <c r="Q10">
         <f>ROUND(Revenue!Q15*Assumptions!$B$11,0)</f>
-        <v>312590.0</v>
+        <v>29895.0</v>
       </c>
       <c r="R10">
         <f>ROUND(Revenue!R15*Assumptions!$B$11,0)</f>
-        <v>329568.0</v>
+        <v>31517.0</v>
       </c>
       <c r="S10">
         <f>ROUND(Revenue!S15*Assumptions!$B$11,0)</f>
-        <v>347441.0</v>
+        <v>33226.0</v>
       </c>
       <c r="T10">
         <f>ROUND(Revenue!T15*Assumptions!$B$11,0)</f>
-        <v>366327.0</v>
+        <v>35032.0</v>
       </c>
       <c r="U10">
         <f>ROUND(Revenue!U15*Assumptions!$B$11,0)</f>
-        <v>386217.0</v>
+        <v>36933.0</v>
       </c>
       <c r="V10">
         <f>ROUND(Revenue!V15*Assumptions!$B$11,0)</f>
-        <v>407183.0</v>
+        <v>38939.0</v>
       </c>
       <c r="W10">
         <f>ROUND(Revenue!W15*Assumptions!$B$11,0)</f>
-        <v>429261.0</v>
+        <v>41051.0</v>
       </c>
       <c r="X10">
         <f>ROUND(Revenue!X15*Assumptions!$B$11,0)</f>
-        <v>452585.0</v>
+        <v>43281.0</v>
       </c>
       <c r="Y10">
         <f>ROUND(Revenue!Y15*Assumptions!$B$11,0)</f>
-        <v>477160.0</v>
+        <v>45632.0</v>
       </c>
       <c r="Z10">
         <f>ROUND(Revenue!Z15*Assumptions!$B$11,0)</f>
-        <v>503041.0</v>
+        <v>48107.0</v>
       </c>
     </row>
     <row r="11">
@@ -2232,59 +2232,59 @@
       </c>
       <c r="M11">
         <f>ROUND(Revenue!M15*Assumptions!$B$16,0)</f>
-        <v>78036.0</v>
+        <v>76295.0</v>
       </c>
       <c r="N11">
         <f>ROUND(Revenue!N15*Assumptions!$B$16,0)</f>
-        <v>82273.0</v>
+        <v>78678.0</v>
       </c>
       <c r="O11">
         <f>ROUND(Revenue!O15*Assumptions!$B$16,0)</f>
-        <v>86734.0</v>
+        <v>82949.0</v>
       </c>
       <c r="P11">
         <f>ROUND(Revenue!P15*Assumptions!$B$16,0)</f>
-        <v>91448.0</v>
+        <v>87459.0</v>
       </c>
       <c r="Q11">
         <f>ROUND(Revenue!Q15*Assumptions!$B$16,0)</f>
-        <v>96413.0</v>
+        <v>92205.0</v>
       </c>
       <c r="R11">
         <f>ROUND(Revenue!R15*Assumptions!$B$16,0)</f>
-        <v>101650.0</v>
+        <v>97210.0</v>
       </c>
       <c r="S11">
         <f>ROUND(Revenue!S15*Assumptions!$B$16,0)</f>
-        <v>107162.0</v>
+        <v>102481.0</v>
       </c>
       <c r="T11">
         <f>ROUND(Revenue!T15*Assumptions!$B$16,0)</f>
-        <v>112987.0</v>
+        <v>108050.0</v>
       </c>
       <c r="U11">
         <f>ROUND(Revenue!U15*Assumptions!$B$16,0)</f>
-        <v>119122.0</v>
+        <v>113914.0</v>
       </c>
       <c r="V11">
         <f>ROUND(Revenue!V15*Assumptions!$B$16,0)</f>
-        <v>125589.0</v>
+        <v>120101.0</v>
       </c>
       <c r="W11">
         <f>ROUND(Revenue!W15*Assumptions!$B$16,0)</f>
-        <v>132398.0</v>
+        <v>126616.0</v>
       </c>
       <c r="X11">
         <f>ROUND(Revenue!X15*Assumptions!$B$16,0)</f>
-        <v>139592.0</v>
+        <v>133493.0</v>
       </c>
       <c r="Y11">
         <f>ROUND(Revenue!Y15*Assumptions!$B$16,0)</f>
-        <v>147172.0</v>
+        <v>140745.0</v>
       </c>
       <c r="Z11">
         <f>ROUND(Revenue!Z15*Assumptions!$B$16,0)</f>
-        <v>155155.0</v>
+        <v>148379.0</v>
       </c>
     </row>
     <row r="12">
@@ -2398,99 +2398,99 @@
       </c>
       <c r="C14">
         <f>C8+C10+C11+C12</f>
-        <v>361261.0</v>
+        <v>227059.0</v>
       </c>
       <c r="D14">
         <f>D8+D10+D11+D12</f>
-        <v>386423.0</v>
+        <v>244926.0</v>
       </c>
       <c r="E14">
         <f>E8+E10+E11+E12</f>
-        <v>412141.0</v>
+        <v>262967.0</v>
       </c>
       <c r="F14">
         <f>F8+F10+F11+F12</f>
-        <v>438447.0</v>
+        <v>281192.0</v>
       </c>
       <c r="G14">
         <f>G8+G10+G11+G12</f>
-        <v>465419.0</v>
+        <v>299625.0</v>
       </c>
       <c r="H14">
         <f>H8+H10+H11+H12</f>
-        <v>493078.0</v>
+        <v>318274.0</v>
       </c>
       <c r="I14">
         <f>I8+I10+I11+I12</f>
-        <v>521452.0</v>
+        <v>337147.0</v>
       </c>
       <c r="J14">
         <f>J8+J10+J11+J12</f>
-        <v>550572.0</v>
+        <v>356254.0</v>
       </c>
       <c r="K14">
         <f>K8+K10+K11+K12</f>
-        <v>580449.0</v>
+        <v>375596.0</v>
       </c>
       <c r="L14">
         <f>L8+L10+L11+L12</f>
-        <v>611212.0</v>
+        <v>395217.0</v>
       </c>
       <c r="M14">
         <f>M8+M10+M11+M12</f>
-        <v>642805.0</v>
+        <v>412792.0</v>
       </c>
       <c r="N14">
         <f>N8+N10+N11+N12</f>
-        <v>675343.0</v>
+        <v>430513.0</v>
       </c>
       <c r="O14">
         <f>O8+O10+O11+O12</f>
-        <v>708837.0</v>
+        <v>450736.0</v>
       </c>
       <c r="P14">
         <f>P8+P10+P11+P12</f>
-        <v>743403.0</v>
+        <v>471276.0</v>
       </c>
       <c r="Q14">
         <f>Q8+Q10+Q11+Q12</f>
-        <v>779032.0</v>
+        <v>492129.0</v>
       </c>
       <c r="R14">
         <f>R8+R10+R11+R12</f>
-        <v>815819.0</v>
+        <v>513328.0</v>
       </c>
       <c r="S14">
         <f>S8+S10+S11+S12</f>
-        <v>853776.0</v>
+        <v>534880.0</v>
       </c>
       <c r="T14">
         <f>T8+T10+T11+T12</f>
-        <v>893059.0</v>
+        <v>556827.0</v>
       </c>
       <c r="U14">
         <f>U8+U10+U11+U12</f>
-        <v>933659.0</v>
+        <v>579167.0</v>
       </c>
       <c r="V14">
         <f>V8+V10+V11+V12</f>
-        <v>975666.0</v>
+        <v>601934.0</v>
       </c>
       <c r="W14">
         <f>W8+W10+W11+W12</f>
-        <v>1019129.0</v>
+        <v>625137.0</v>
       </c>
       <c r="X14">
         <f>X8+X10+X11+X12</f>
-        <v>1064224.0</v>
+        <v>648821.0</v>
       </c>
       <c r="Y14">
         <f>Y8+Y10+Y11+Y12</f>
-        <v>1110957.0</v>
+        <v>673002.0</v>
       </c>
       <c r="Z14">
         <f>Z8+Z10+Z11+Z12</f>
-        <v>1159399.0</v>
+        <v>697689.0</v>
       </c>
     </row>
   </sheetData>
@@ -2670,63 +2670,63 @@
       </c>
       <c r="M5">
         <f>Revenue!M15</f>
-        <v>974237.0</v>
+        <v>952503.0</v>
       </c>
       <c r="N5">
         <f>Revenue!N15</f>
-        <v>1027125.0</v>
+        <v>982242.0</v>
       </c>
       <c r="O5">
         <f>Revenue!O15</f>
-        <v>1082825.0</v>
+        <v>1035569.0</v>
       </c>
       <c r="P5">
         <f>Revenue!P15</f>
-        <v>1141678.0</v>
+        <v>1091872.0</v>
       </c>
       <c r="Q5">
         <f>Revenue!Q15</f>
-        <v>1203659.0</v>
+        <v>1151128.0</v>
       </c>
       <c r="R5">
         <f>Revenue!R15</f>
-        <v>1269035.0</v>
+        <v>1213602.0</v>
       </c>
       <c r="S5">
         <f>Revenue!S15</f>
-        <v>1337854.0</v>
+        <v>1279415.0</v>
       </c>
       <c r="T5">
         <f>Revenue!T15</f>
-        <v>1410578.0</v>
+        <v>1348943.0</v>
       </c>
       <c r="U5">
         <f>Revenue!U15</f>
-        <v>1487166.0</v>
+        <v>1422150.0</v>
       </c>
       <c r="V5">
         <f>Revenue!V15</f>
-        <v>1567898.0</v>
+        <v>1499390.0</v>
       </c>
       <c r="W5">
         <f>Revenue!W15</f>
-        <v>1652912.0</v>
+        <v>1580722.0</v>
       </c>
       <c r="X5">
         <f>Revenue!X15</f>
-        <v>1742724.0</v>
+        <v>1666574.0</v>
       </c>
       <c r="Y5">
         <f>Revenue!Y15</f>
-        <v>1837349.0</v>
+        <v>1757119.0</v>
       </c>
       <c r="Z5">
         <f>Revenue!Z15</f>
-        <v>1937010.0</v>
+        <v>1852424.0</v>
       </c>
       <c r="AA5">
         <f>SUM(C5:Z5)</f>
-        <v>27040365.0</v>
+        <v>26201968.0</v>
       </c>
     </row>
     <row r="6">
@@ -2737,103 +2737,103 @@
       </c>
       <c r="C6">
         <f>-Costs!C10</f>
-        <v>-149113.0</v>
+        <v>-14911.0</v>
       </c>
       <c r="D6">
         <f>-Costs!D10</f>
-        <v>-157219.0</v>
+        <v>-15722.0</v>
       </c>
       <c r="E6">
         <f>-Costs!E10</f>
-        <v>-165749.0</v>
+        <v>-16575.0</v>
       </c>
       <c r="F6">
         <f>-Costs!F10</f>
-        <v>-174728.0</v>
+        <v>-17473.0</v>
       </c>
       <c r="G6">
         <f>-Costs!G10</f>
-        <v>-184215.0</v>
+        <v>-18421.0</v>
       </c>
       <c r="H6">
         <f>-Costs!H10</f>
-        <v>-194227.0</v>
+        <v>-19423.0</v>
       </c>
       <c r="I6">
         <f>-Costs!I10</f>
-        <v>-204783.0</v>
+        <v>-20478.0</v>
       </c>
       <c r="J6">
         <f>-Costs!J10</f>
-        <v>-215909.0</v>
+        <v>-21591.0</v>
       </c>
       <c r="K6">
         <f>-Costs!K10</f>
-        <v>-227614.0</v>
+        <v>-22761.0</v>
       </c>
       <c r="L6">
         <f>-Costs!L10</f>
-        <v>-239994.0</v>
+        <v>-23999.0</v>
       </c>
       <c r="M6">
         <f>-Costs!M10</f>
-        <v>-253009.0</v>
+        <v>-24737.0</v>
       </c>
       <c r="N6">
         <f>-Costs!N10</f>
-        <v>-266744.0</v>
+        <v>-25509.0</v>
       </c>
       <c r="O6">
         <f>-Costs!O10</f>
-        <v>-281210.0</v>
+        <v>-26894.0</v>
       </c>
       <c r="P6">
         <f>-Costs!P10</f>
-        <v>-296494.0</v>
+        <v>-28356.0</v>
       </c>
       <c r="Q6">
         <f>-Costs!Q10</f>
-        <v>-312590.0</v>
+        <v>-29895.0</v>
       </c>
       <c r="R6">
         <f>-Costs!R10</f>
-        <v>-329568.0</v>
+        <v>-31517.0</v>
       </c>
       <c r="S6">
         <f>-Costs!S10</f>
-        <v>-347441.0</v>
+        <v>-33226.0</v>
       </c>
       <c r="T6">
         <f>-Costs!T10</f>
-        <v>-366327.0</v>
+        <v>-35032.0</v>
       </c>
       <c r="U6">
         <f>-Costs!U10</f>
-        <v>-386217.0</v>
+        <v>-36933.0</v>
       </c>
       <c r="V6">
         <f>-Costs!V10</f>
-        <v>-407183.0</v>
+        <v>-38939.0</v>
       </c>
       <c r="W6">
         <f>-Costs!W10</f>
-        <v>-429261.0</v>
+        <v>-41051.0</v>
       </c>
       <c r="X6">
         <f>-Costs!X10</f>
-        <v>-452585.0</v>
+        <v>-43281.0</v>
       </c>
       <c r="Y6">
         <f>-Costs!Y10</f>
-        <v>-477160.0</v>
+        <v>-45632.0</v>
       </c>
       <c r="Z6">
         <f>-Costs!Z10</f>
-        <v>-503041.0</v>
+        <v>-48107.0</v>
       </c>
       <c r="AA6">
         <f>SUM(C6:Z6)</f>
-        <v>-7022381.0</v>
+        <v>-680463.0</v>
       </c>
     </row>
     <row r="7">
@@ -2844,103 +2844,103 @@
       </c>
       <c r="C7">
         <f>C5+C6</f>
-        <v>425062.0</v>
+        <v>559264.0</v>
       </c>
       <c r="D7">
         <f>D5+D6</f>
-        <v>448169.0</v>
+        <v>589666.0</v>
       </c>
       <c r="E7">
         <f>E5+E6</f>
-        <v>472485.0</v>
+        <v>621659.0</v>
       </c>
       <c r="F7">
         <f>F5+F6</f>
-        <v>498078.0</v>
+        <v>655333.0</v>
       </c>
       <c r="G7">
         <f>G5+G6</f>
-        <v>525121.0</v>
+        <v>690915.0</v>
       </c>
       <c r="H7">
         <f>H5+H6</f>
-        <v>553663.0</v>
+        <v>728467.0</v>
       </c>
       <c r="I7">
         <f>I5+I6</f>
-        <v>583755.0</v>
+        <v>768060.0</v>
       </c>
       <c r="J7">
         <f>J5+J6</f>
-        <v>615471.0</v>
+        <v>809789.0</v>
       </c>
       <c r="K7">
         <f>K5+K6</f>
-        <v>648835.0</v>
+        <v>853688.0</v>
       </c>
       <c r="L7">
         <f>L5+L6</f>
-        <v>684125.0</v>
+        <v>900120.0</v>
       </c>
       <c r="M7">
         <f>M5+M6</f>
-        <v>721228.0</v>
+        <v>927766.0</v>
       </c>
       <c r="N7">
         <f>N5+N6</f>
-        <v>760381.0</v>
+        <v>956733.0</v>
       </c>
       <c r="O7">
         <f>O5+O6</f>
-        <v>801615.0</v>
+        <v>1008675.0</v>
       </c>
       <c r="P7">
         <f>P5+P6</f>
-        <v>845184.0</v>
+        <v>1063516.0</v>
       </c>
       <c r="Q7">
         <f>Q5+Q6</f>
-        <v>891069.0</v>
+        <v>1121233.0</v>
       </c>
       <c r="R7">
         <f>R5+R6</f>
-        <v>939467.0</v>
+        <v>1182085.0</v>
       </c>
       <c r="S7">
         <f>S5+S6</f>
-        <v>990413.0</v>
+        <v>1246189.0</v>
       </c>
       <c r="T7">
         <f>T5+T6</f>
-        <v>1044251.0</v>
+        <v>1313911.0</v>
       </c>
       <c r="U7">
         <f>U5+U6</f>
-        <v>1100949.0</v>
+        <v>1385217.0</v>
       </c>
       <c r="V7">
         <f>V5+V6</f>
-        <v>1160715.0</v>
+        <v>1460451.0</v>
       </c>
       <c r="W7">
         <f>W5+W6</f>
-        <v>1223651.0</v>
+        <v>1539671.0</v>
       </c>
       <c r="X7">
         <f>X5+X6</f>
-        <v>1290139.0</v>
+        <v>1623293.0</v>
       </c>
       <c r="Y7">
         <f>Y5+Y6</f>
-        <v>1360189.0</v>
+        <v>1711487.0</v>
       </c>
       <c r="Z7">
         <f>Z5+Z6</f>
-        <v>1433969.0</v>
+        <v>1804317.0</v>
       </c>
       <c r="AA7">
         <f>SUM(C7:Z7)</f>
-        <v>20017984.0</v>
+        <v>25521505.0</v>
       </c>
     </row>
     <row r="8">
@@ -2951,99 +2951,99 @@
       </c>
       <c r="C8">
         <f>IF(C5=0,0,ROUND(C7/C5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="D8">
         <f>IF(D5=0,0,ROUND(D7/D5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="E8">
         <f>IF(E5=0,0,ROUND(E7/E5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="F8">
         <f>IF(F5=0,0,ROUND(F7/F5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="G8">
         <f>IF(G5=0,0,ROUND(G7/G5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="H8">
         <f>IF(H5=0,0,ROUND(H7/H5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="I8">
         <f>IF(I5=0,0,ROUND(I7/I5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="J8">
         <f>IF(J5=0,0,ROUND(J7/J5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="K8">
         <f>IF(K5=0,0,ROUND(K7/K5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="L8">
         <f>IF(L5=0,0,ROUND(L7/L5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="M8">
         <f>IF(M5=0,0,ROUND(M7/M5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="N8">
         <f>IF(N5=0,0,ROUND(N7/N5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="O8">
         <f>IF(O5=0,0,ROUND(O7/O5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="P8">
         <f>IF(P5=0,0,ROUND(P7/P5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="Q8">
         <f>IF(Q5=0,0,ROUND(Q7/Q5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="R8">
         <f>IF(R5=0,0,ROUND(R7/R5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="S8">
         <f>IF(S5=0,0,ROUND(S7/S5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="T8">
         <f>IF(T5=0,0,ROUND(T7/T5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="U8">
         <f>IF(U5=0,0,ROUND(U7/U5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="V8">
         <f>IF(V5=0,0,ROUND(V7/V5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="W8">
         <f>IF(W5=0,0,ROUND(W7/W5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="X8">
         <f>IF(X5=0,0,ROUND(X7/X5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="Y8">
         <f>IF(Y5=0,0,ROUND(Y7/Y5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
       <c r="Z8">
         <f>IF(Z5=0,0,ROUND(Z7/Z5,4))</f>
-        <v>0.7403</v>
+        <v>0.974</v>
       </c>
     </row>
     <row r="10">
@@ -3201,63 +3201,63 @@
       </c>
       <c r="M11">
         <f>-Costs!M11</f>
-        <v>-78036.0</v>
+        <v>-76295.0</v>
       </c>
       <c r="N11">
         <f>-Costs!N11</f>
-        <v>-82273.0</v>
+        <v>-78678.0</v>
       </c>
       <c r="O11">
         <f>-Costs!O11</f>
-        <v>-86734.0</v>
+        <v>-82949.0</v>
       </c>
       <c r="P11">
         <f>-Costs!P11</f>
-        <v>-91448.0</v>
+        <v>-87459.0</v>
       </c>
       <c r="Q11">
         <f>-Costs!Q11</f>
-        <v>-96413.0</v>
+        <v>-92205.0</v>
       </c>
       <c r="R11">
         <f>-Costs!R11</f>
-        <v>-101650.0</v>
+        <v>-97210.0</v>
       </c>
       <c r="S11">
         <f>-Costs!S11</f>
-        <v>-107162.0</v>
+        <v>-102481.0</v>
       </c>
       <c r="T11">
         <f>-Costs!T11</f>
-        <v>-112987.0</v>
+        <v>-108050.0</v>
       </c>
       <c r="U11">
         <f>-Costs!U11</f>
-        <v>-119122.0</v>
+        <v>-113914.0</v>
       </c>
       <c r="V11">
         <f>-Costs!V11</f>
-        <v>-125589.0</v>
+        <v>-120101.0</v>
       </c>
       <c r="W11">
         <f>-Costs!W11</f>
-        <v>-132398.0</v>
+        <v>-126616.0</v>
       </c>
       <c r="X11">
         <f>-Costs!X11</f>
-        <v>-139592.0</v>
+        <v>-133493.0</v>
       </c>
       <c r="Y11">
         <f>-Costs!Y11</f>
-        <v>-147172.0</v>
+        <v>-140745.0</v>
       </c>
       <c r="Z11">
         <f>-Costs!Z11</f>
-        <v>-155155.0</v>
+        <v>-148379.0</v>
       </c>
       <c r="AA11">
         <f>SUM(C11:Z11)</f>
-        <v>-2165935.0</v>
+        <v>-2098779.0</v>
       </c>
     </row>
     <row r="12">
@@ -3415,63 +3415,63 @@
       </c>
       <c r="M13">
         <f>M10+M11+M12</f>
-        <v>-389796.0</v>
+        <v>-388055.0</v>
       </c>
       <c r="N13">
         <f>N10+N11+N12</f>
-        <v>-408599.0</v>
+        <v>-405004.0</v>
       </c>
       <c r="O13">
         <f>O10+O11+O12</f>
-        <v>-427627.0</v>
+        <v>-423842.0</v>
       </c>
       <c r="P13">
         <f>P10+P11+P12</f>
-        <v>-446909.0</v>
+        <v>-442920.0</v>
       </c>
       <c r="Q13">
         <f>Q10+Q11+Q12</f>
-        <v>-466442.0</v>
+        <v>-462234.0</v>
       </c>
       <c r="R13">
         <f>R10+R11+R12</f>
-        <v>-486251.0</v>
+        <v>-481811.0</v>
       </c>
       <c r="S13">
         <f>S10+S11+S12</f>
-        <v>-506335.0</v>
+        <v>-501654.0</v>
       </c>
       <c r="T13">
         <f>T10+T11+T12</f>
-        <v>-526732.0</v>
+        <v>-521795.0</v>
       </c>
       <c r="U13">
         <f>U10+U11+U12</f>
-        <v>-547442.0</v>
+        <v>-542234.0</v>
       </c>
       <c r="V13">
         <f>V10+V11+V12</f>
-        <v>-568483.0</v>
+        <v>-562995.0</v>
       </c>
       <c r="W13">
         <f>W10+W11+W12</f>
-        <v>-589868.0</v>
+        <v>-584086.0</v>
       </c>
       <c r="X13">
         <f>X10+X11+X12</f>
-        <v>-611639.0</v>
+        <v>-605540.0</v>
       </c>
       <c r="Y13">
         <f>Y10+Y11+Y12</f>
-        <v>-633797.0</v>
+        <v>-627370.0</v>
       </c>
       <c r="Z13">
         <f>Z10+Z11+Z12</f>
-        <v>-656358.0</v>
+        <v>-649582.0</v>
       </c>
       <c r="AA13">
         <f>SUM(C13:Z13)</f>
-        <v>-10173181.0</v>
+        <v>-10106025.0</v>
       </c>
     </row>
     <row r="15">
@@ -3482,103 +3482,103 @@
       </c>
       <c r="C15">
         <f>C7+C13</f>
-        <v>212914.0</v>
+        <v>347116.0</v>
       </c>
       <c r="D15">
         <f>D7+D13</f>
-        <v>218965.0</v>
+        <v>360462.0</v>
       </c>
       <c r="E15">
         <f>E7+E13</f>
-        <v>226093.0</v>
+        <v>375267.0</v>
       </c>
       <c r="F15">
         <f>F7+F13</f>
-        <v>234359.0</v>
+        <v>391614.0</v>
       </c>
       <c r="G15">
         <f>G7+G13</f>
-        <v>243917.0</v>
+        <v>409711.0</v>
       </c>
       <c r="H15">
         <f>H7+H13</f>
-        <v>254812.0</v>
+        <v>429616.0</v>
       </c>
       <c r="I15">
         <f>I7+I13</f>
-        <v>267086.0</v>
+        <v>451391.0</v>
       </c>
       <c r="J15">
         <f>J7+J13</f>
-        <v>280808.0</v>
+        <v>475126.0</v>
       </c>
       <c r="K15">
         <f>K7+K13</f>
-        <v>296000.0</v>
+        <v>500853.0</v>
       </c>
       <c r="L15">
         <f>L7+L13</f>
-        <v>312907.0</v>
+        <v>528902.0</v>
       </c>
       <c r="M15">
         <f>M7+M13</f>
-        <v>331432.0</v>
+        <v>539711.0</v>
       </c>
       <c r="N15">
         <f>N7+N13</f>
-        <v>351782.0</v>
+        <v>551729.0</v>
       </c>
       <c r="O15">
         <f>O7+O13</f>
-        <v>373988.0</v>
+        <v>584833.0</v>
       </c>
       <c r="P15">
         <f>P7+P13</f>
-        <v>398275.0</v>
+        <v>620596.0</v>
       </c>
       <c r="Q15">
         <f>Q7+Q13</f>
-        <v>424627.0</v>
+        <v>658999.0</v>
       </c>
       <c r="R15">
         <f>R7+R13</f>
-        <v>453216.0</v>
+        <v>700274.0</v>
       </c>
       <c r="S15">
         <f>S7+S13</f>
-        <v>484078.0</v>
+        <v>744535.0</v>
       </c>
       <c r="T15">
         <f>T7+T13</f>
-        <v>517519.0</v>
+        <v>792116.0</v>
       </c>
       <c r="U15">
         <f>U7+U13</f>
-        <v>553507.0</v>
+        <v>842983.0</v>
       </c>
       <c r="V15">
         <f>V7+V13</f>
-        <v>592232.0</v>
+        <v>897456.0</v>
       </c>
       <c r="W15">
         <f>W7+W13</f>
-        <v>633783.0</v>
+        <v>955585.0</v>
       </c>
       <c r="X15">
         <f>X7+X13</f>
-        <v>678500.0</v>
+        <v>1017753.0</v>
       </c>
       <c r="Y15">
         <f>Y7+Y13</f>
-        <v>726392.0</v>
+        <v>1084117.0</v>
       </c>
       <c r="Z15">
         <f>Z7+Z13</f>
-        <v>777611.0</v>
+        <v>1154735.0</v>
       </c>
       <c r="AA15">
         <f>SUM(C15:Z15)</f>
-        <v>9844803.0</v>
+        <v>15415480.0</v>
       </c>
     </row>
     <row r="16">
@@ -3589,99 +3589,99 @@
       </c>
       <c r="C16">
         <f>IF(C5=0,0,ROUND(C15/C5,4))</f>
-        <v>0.3708</v>
+        <v>0.6045</v>
       </c>
       <c r="D16">
         <f>IF(D5=0,0,ROUND(D15/D5,4))</f>
-        <v>0.3617</v>
+        <v>0.5954</v>
       </c>
       <c r="E16">
         <f>IF(E5=0,0,ROUND(E15/E5,4))</f>
-        <v>0.3542</v>
+        <v>0.588</v>
       </c>
       <c r="F16">
         <f>IF(F5=0,0,ROUND(F15/F5,4))</f>
-        <v>0.3483</v>
+        <v>0.5821</v>
       </c>
       <c r="G16">
         <f>IF(G5=0,0,ROUND(G15/G5,4))</f>
-        <v>0.3439</v>
+        <v>0.5776</v>
       </c>
       <c r="H16">
         <f>IF(H5=0,0,ROUND(H15/H5,4))</f>
-        <v>0.3407</v>
+        <v>0.5744</v>
       </c>
       <c r="I16">
         <f>IF(I5=0,0,ROUND(I15/I5,4))</f>
-        <v>0.3387</v>
+        <v>0.5724</v>
       </c>
       <c r="J16">
         <f>IF(J5=0,0,ROUND(J15/J5,4))</f>
-        <v>0.3378</v>
+        <v>0.5715</v>
       </c>
       <c r="K16">
         <f>IF(K5=0,0,ROUND(K15/K5,4))</f>
-        <v>0.3377</v>
+        <v>0.5715</v>
       </c>
       <c r="L16">
         <f>IF(L5=0,0,ROUND(L15/L5,4))</f>
-        <v>0.3386</v>
+        <v>0.5723</v>
       </c>
       <c r="M16">
         <f>IF(M5=0,0,ROUND(M15/M5,4))</f>
-        <v>0.3402</v>
+        <v>0.5666</v>
       </c>
       <c r="N16">
         <f>IF(N5=0,0,ROUND(N15/N5,4))</f>
-        <v>0.3425</v>
+        <v>0.5617</v>
       </c>
       <c r="O16">
         <f>IF(O5=0,0,ROUND(O15/O5,4))</f>
-        <v>0.3454</v>
+        <v>0.5647</v>
       </c>
       <c r="P16">
         <f>IF(P5=0,0,ROUND(P15/P5,4))</f>
-        <v>0.3489</v>
+        <v>0.5684</v>
       </c>
       <c r="Q16">
         <f>IF(Q5=0,0,ROUND(Q15/Q5,4))</f>
-        <v>0.3528</v>
+        <v>0.5725</v>
       </c>
       <c r="R16">
         <f>IF(R5=0,0,ROUND(R15/R5,4))</f>
-        <v>0.3571</v>
+        <v>0.577</v>
       </c>
       <c r="S16">
         <f>IF(S5=0,0,ROUND(S15/S5,4))</f>
-        <v>0.3618</v>
+        <v>0.5819</v>
       </c>
       <c r="T16">
         <f>IF(T5=0,0,ROUND(T15/T5,4))</f>
-        <v>0.3669</v>
+        <v>0.5872</v>
       </c>
       <c r="U16">
         <f>IF(U5=0,0,ROUND(U15/U5,4))</f>
-        <v>0.3722</v>
+        <v>0.5928</v>
       </c>
       <c r="V16">
         <f>IF(V5=0,0,ROUND(V15/V5,4))</f>
-        <v>0.3777</v>
+        <v>0.5985</v>
       </c>
       <c r="W16">
         <f>IF(W5=0,0,ROUND(W15/W5,4))</f>
-        <v>0.3834</v>
+        <v>0.6045</v>
       </c>
       <c r="X16">
         <f>IF(X5=0,0,ROUND(X15/X5,4))</f>
-        <v>0.3893</v>
+        <v>0.6107</v>
       </c>
       <c r="Y16">
         <f>IF(Y5=0,0,ROUND(Y15/Y5,4))</f>
-        <v>0.3953</v>
+        <v>0.617</v>
       </c>
       <c r="Z16">
         <f>IF(Z5=0,0,ROUND(Z15/Z5,4))</f>
-        <v>0.4014</v>
+        <v>0.6234</v>
       </c>
     </row>
     <row r="18">
@@ -3692,99 +3692,99 @@
       </c>
       <c r="C18">
         <f>C15</f>
-        <v>212914.0</v>
+        <v>347116.0</v>
       </c>
       <c r="D18">
         <f>C18+D15</f>
-        <v>431879.0</v>
+        <v>707578.0</v>
       </c>
       <c r="E18">
         <f>D18+E15</f>
-        <v>657972.0</v>
+        <v>1082845.0</v>
       </c>
       <c r="F18">
         <f>E18+F15</f>
-        <v>892331.0</v>
+        <v>1474459.0</v>
       </c>
       <c r="G18">
         <f>F18+G15</f>
-        <v>1136248.0</v>
+        <v>1884170.0</v>
       </c>
       <c r="H18">
         <f>G18+H15</f>
-        <v>1391060.0</v>
+        <v>2313786.0</v>
       </c>
       <c r="I18">
         <f>H18+I15</f>
-        <v>1658146.0</v>
+        <v>2765177.0</v>
       </c>
       <c r="J18">
         <f>I18+J15</f>
-        <v>1938954.0</v>
+        <v>3240303.0</v>
       </c>
       <c r="K18">
         <f>J18+K15</f>
-        <v>2234954.0</v>
+        <v>3741156.0</v>
       </c>
       <c r="L18">
         <f>K18+L15</f>
-        <v>2547861.0</v>
+        <v>4270058.0</v>
       </c>
       <c r="M18">
         <f>L18+M15</f>
-        <v>2879293.0</v>
+        <v>4809769.0</v>
       </c>
       <c r="N18">
         <f>M18+N15</f>
-        <v>3231075.0</v>
+        <v>5361498.0</v>
       </c>
       <c r="O18">
         <f>N18+O15</f>
-        <v>3605063.0</v>
+        <v>5946331.0</v>
       </c>
       <c r="P18">
         <f>O18+P15</f>
-        <v>4003338.0</v>
+        <v>6566927.0</v>
       </c>
       <c r="Q18">
         <f>P18+Q15</f>
-        <v>4427965.0</v>
+        <v>7225926.0</v>
       </c>
       <c r="R18">
         <f>Q18+R15</f>
-        <v>4881181.0</v>
+        <v>7926200.0</v>
       </c>
       <c r="S18">
         <f>R18+S15</f>
-        <v>5365259.0</v>
+        <v>8670735.0</v>
       </c>
       <c r="T18">
         <f>S18+T15</f>
-        <v>5882778.0</v>
+        <v>9462851.0</v>
       </c>
       <c r="U18">
         <f>T18+U15</f>
-        <v>6436285.0</v>
+        <v>10305834.0</v>
       </c>
       <c r="V18">
         <f>U18+V15</f>
-        <v>7028517.0</v>
+        <v>11203290.0</v>
       </c>
       <c r="W18">
         <f>V18+W15</f>
-        <v>7662300.0</v>
+        <v>12158875.0</v>
       </c>
       <c r="X18">
         <f>W18+X15</f>
-        <v>8340800.0</v>
+        <v>13176628.0</v>
       </c>
       <c r="Y18">
         <f>X18+Y15</f>
-        <v>9067192.0</v>
+        <v>14260745.0</v>
       </c>
       <c r="Z18">
         <f>Y18+Z15</f>
-        <v>9844803.0</v>
+        <v>15415480.0</v>
       </c>
     </row>
   </sheetData>
@@ -3816,7 +3816,7 @@
       </c>
       <c r="B3">
         <f>Revenue!Z17</f>
-        <v>27040365.0</v>
+        <v>26201968.0</v>
       </c>
     </row>
     <row r="4">
@@ -3827,7 +3827,7 @@
       </c>
       <c r="B4">
         <f>'P&amp;L'!AA15</f>
-        <v>9844803.0</v>
+        <v>15415480.0</v>
       </c>
     </row>
     <row r="5">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="B5">
         <f>SUM('P&amp;L'!O15:Z15)</f>
-        <v>6613728.0</v>
+        <v>10053982.0</v>
       </c>
     </row>
     <row r="6">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="B7">
         <f>ROUND(B5*B6,0)</f>
-        <v>84655718.0</v>
+        <v>128690970.0</v>
       </c>
     </row>
     <row r="8">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="B9">
         <f>B7-B8</f>
-        <v>82405718.0</v>
+        <v>126440970.0</v>
       </c>
     </row>
     <row r="11">
@@ -3893,7 +3893,7 @@
       </c>
       <c r="B11">
         <f>AVERAGE('P&amp;L'!C15:Z15)</f>
-        <v>410200.125</v>
+        <v>642311.6666666666</v>
       </c>
     </row>
     <row r="12">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="B12">
         <f>MAX('P&amp;L'!C15:Z15)</f>
-        <v>777611.0</v>
+        <v>1154735.0</v>
       </c>
     </row>
     <row r="13">
@@ -3915,7 +3915,7 @@
       </c>
       <c r="B13">
         <f>MIN('P&amp;L'!C15:Z15)</f>
-        <v>212914.0</v>
+        <v>347116.0</v>
       </c>
     </row>
     <row r="14">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="B14">
         <f>SUMIF('P&amp;L'!C15:Z15,"&gt;0")</f>
-        <v>9844803.0</v>
+        <v>15415480.0</v>
       </c>
     </row>
     <row r="15">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="B15">
         <f>ABS(B12-B13)</f>
-        <v>564697.0</v>
+        <v>807619.0</v>
       </c>
     </row>
   </sheetData>
